--- a/data/satisfaction_summary/2026/1-9月/1-9月客户类型满意度汇总表.xlsx
+++ b/data/satisfaction_summary/2026/1-9月/1-9月客户类型满意度汇总表.xlsx
@@ -586,22 +586,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>9.470000000000001</v>
+        <v>9.48</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>9.859999999999999</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>9.470000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>9.710000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>8.83</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
@@ -1159,7 +1159,7 @@
         <v>9.550000000000001</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>9.68</v>
+        <v>9.69</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>9.460000000000001</v>
